--- a/txt/Book1.xlsx
+++ b/txt/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/giinhancom_0513/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1140882C-C9A5-FA4E-B879-367BA2838EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA07861-B2C7-334C-B39D-0AA12466F786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3080" yWindow="2160" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
+    <workbookView xWindow="2920" yWindow="3580" windowWidth="28040" windowHeight="17180" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
   <si>
     <t>category</t>
   </si>
@@ -48,24 +48,6 @@
     <t>card</t>
   </si>
   <si>
-    <t>txt</t>
-  </si>
-  <si>
-    <t>일일</t>
-  </si>
-  <si>
-    <t>이일</t>
-  </si>
-  <si>
-    <t>삼일</t>
-  </si>
-  <si>
-    <t>사일</t>
-  </si>
-  <si>
-    <t>오일</t>
-  </si>
-  <si>
     <t>한지인</t>
   </si>
   <si>
@@ -73,13 +55,68 @@
   </si>
   <si>
     <t>나는 한지인이다</t>
+  </si>
+  <si>
+    <t>컨설팅 신청하기</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>파타고니아 코리아 환경 캠페인 "지천구곡: 우리를 살게하는 강"</t>
+  </si>
+  <si>
+    <t>파타고니아 코리아가 힘을 실어주는 댐 건설 반대 캠페인을 함께 제작했습니다. 지천은 너무나 아름다운 것들이 풍성하게 담겨있는 충청남도 청양의 소중한 물입니다. 흐르는 구석구석마다 사람과 동물, 식물- 모든 생명에게 살아갈 힘과 재료를 아낌없이 주는 지천을 지키기 위해 오랫동안 이어온 이야기에 파타고니아 코리아, 그리고 여러 동료들과 함께 힘을 실어 바이럴을 만들고 서명을 모아 전달했습니다. 
+캠페인 사이트
+https://www.patagonia.co.kr/activismHub/JiRiver
+제작 항목 | 캠페인 숏츠/릴스 5편, 웹사이트 이미지, 포스터, 리플렛
+기획 | 오늘의풍경 신인아, 한지인, 팀도밍고 김도형
+인터뷰&amp;버벌브랜딩 | 한지인
+영상 | 팀도밍고 김도형, 김하연, 오수민, 심현빈
+사진 | 임효진
+디자인 | 신인아, 김영인
+레터링 | 박부미
+협조 | 마을문화연구소 김명숙, 위로책방 이민주, 청양전통시장상인회장 심준보, 푸드카빙 정길순, 농부 김진환</t>
+  </si>
+  <si>
+    <t>create</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>operate</t>
+  </si>
+  <si>
+    <t>write</t>
+  </si>
+  <si>
+    <t>talk</t>
+  </si>
+  <si>
+    <t>consult</t>
+  </si>
+  <si>
+    <t>back heading</t>
+  </si>
+  <si>
+    <t>back  body</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -91,6 +128,13 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -117,9 +161,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -455,73 +511,189 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2E46E7-1DAD-934D-9C92-FF8655A6E484}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="43.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.6640625" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="4"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B17" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B22" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
+    <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -531,22 +703,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B72D82-9823-C241-8645-4BCD8A0E8126}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/txt/Book1.xlsx
+++ b/txt/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/giinhancom_0513/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA07861-B2C7-334C-B39D-0AA12466F786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFDADE7-A8E0-5D49-9325-9BA810459230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2920" yWindow="3580" windowWidth="28040" windowHeight="17180" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
+    <workbookView xWindow="2920" yWindow="3160" windowWidth="28040" windowHeight="17180" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
   <si>
     <t>category</t>
   </si>
@@ -63,15 +63,82 @@
     <t>01</t>
   </si>
   <si>
-    <t>파타고니아 코리아 환경 캠페인 "지천구곡: 우리를 살게하는 강"</t>
+    <t>create</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>operate</t>
+  </si>
+  <si>
+    <t>write</t>
+  </si>
+  <si>
+    <t>talk</t>
+  </si>
+  <si>
+    <t>consult</t>
+  </si>
+  <si>
+    <t>back heading</t>
+  </si>
+  <si>
+    <t>back  body</t>
+  </si>
+  <si>
+    <t>tag 1</t>
+  </si>
+  <si>
+    <t>tag 2</t>
+  </si>
+  <si>
+    <t>tag 3</t>
+  </si>
+  <si>
+    <t>interviewer</t>
+  </si>
+  <si>
+    <t>writer</t>
+  </si>
+  <si>
+    <t>manager</t>
+  </si>
+  <si>
+    <t>작은 마켓과 페어가 곳곳에서 일어나는 시절을 지나며 중고 물품을 사고파는 플리마켓의 의미에 대해 이야기를 나누다 탄생한 ‘마켓아닌 마켓’입니다. 소유가 사람의 정체성에 지대한 영향을 미치고 있는 시점에서, 소유한 것을 재판매하는 행위는 곳 소유주의 정체성을 해체하고 재배열한다는 의미를 가지고 있습니다. 이러한 관점에 동의하는 8명(팀)이 모여 판매와 더불어 ‘적극적 물물 교환’ 방식을 경험하며 ‘가치의 교환에 대한 합의점을 찾는다’는 미션을 실행했습니다. 
+무언가를 ‘제대로’ 소유하는 삶을 권장하는 언마켓의 다음을 기대합니다.
+언마켓 계정
+https://www.instagram.com/un_mark.et/
+호스트 | 한지인
+코호스트 | 제비, 다정
+참여 셀러 | 지인, 제비, 다정, 현인, 진, 단단, 예지, 벗밭, 슭</t>
+  </si>
+  <si>
+    <t>언마켓 un-market
+해체와 재배열 life pieces, re-rooting</t>
+  </si>
+  <si>
+    <t>PM</t>
+  </si>
+  <si>
+    <t>designer</t>
   </si>
   <si>
     <t>파타고니아 코리아가 힘을 실어주는 댐 건설 반대 캠페인을 함께 제작했습니다. 지천은 너무나 아름다운 것들이 풍성하게 담겨있는 충청남도 청양의 소중한 물입니다. 흐르는 구석구석마다 사람과 동물, 식물- 모든 생명에게 살아갈 힘과 재료를 아낌없이 주는 지천을 지키기 위해 오랫동안 이어온 이야기에 파타고니아 코리아, 그리고 여러 동료들과 함께 힘을 실어 바이럴을 만들고 서명을 모아 전달했습니다. 
+캠페인 사이트를 방문하셔서 5개의 영상을 감상하시고 댓글로 응원을 남겨주세요.
 캠페인 사이트
 https://www.patagonia.co.kr/activismHub/JiRiver
-제작 항목 | 캠페인 숏츠/릴스 5편, 웹사이트 이미지, 포스터, 리플렛
 기획 | 오늘의풍경 신인아, 한지인, 팀도밍고 김도형
-인터뷰&amp;버벌브랜딩 | 한지인
+인터뷰 &amp; 버벌 브랜딩 | 한지인
 영상 | 팀도밍고 김도형, 김하연, 오수민, 심현빈
 사진 | 임효진
 디자인 | 신인아, 김영인
@@ -79,44 +146,16 @@
 협조 | 마을문화연구소 김명숙, 위로책방 이민주, 청양전통시장상인회장 심준보, 푸드카빙 정길순, 농부 김진환</t>
   </si>
   <si>
-    <t>create</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>operate</t>
-  </si>
-  <si>
-    <t>write</t>
-  </si>
-  <si>
-    <t>talk</t>
-  </si>
-  <si>
-    <t>consult</t>
-  </si>
-  <si>
-    <t>back heading</t>
-  </si>
-  <si>
-    <t>back  body</t>
+    <t>파타고니아 코리아
+환경 캠페인
+지천구곡:우리를 살게하는 강</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -139,13 +178,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -161,7 +213,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -175,6 +227,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -511,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2E46E7-1DAD-934D-9C92-FF8655A6E484}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.83203125" style="2" customWidth="1"/>
@@ -521,58 +582,88 @@
     <col min="5" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G1" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="C3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="3" t="s">
+    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2</v>
       </c>
@@ -580,30 +671,30 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>3</v>
       </c>
@@ -611,27 +702,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="3" t="s">
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="3" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -644,25 +735,25 @@
     </row>
     <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -675,25 +766,25 @@
     </row>
     <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/txt/Book1.xlsx
+++ b/txt/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/giinhancom_0513/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFDADE7-A8E0-5D49-9325-9BA810459230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33F3DF2-01D9-8741-8672-9AE76DCE14A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2920" yWindow="3160" windowWidth="28040" windowHeight="17180" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
+    <workbookView xWindow="14860" yWindow="2800" windowWidth="28040" windowHeight="17180" xr2:uid="{F0124784-7F58-C742-B935-DD8D6B76A885}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t>category</t>
   </si>
@@ -150,12 +150,54 @@
 환경 캠페인
 지천구곡:우리를 살게하는 강</t>
   </si>
+  <si>
+    <t>아름답지만 피곤한
+남방큰돌고래</t>
+  </si>
+  <si>
+    <t>artist</t>
+  </si>
+  <si>
+    <t>바다거북 시민참여과학
+결과보고와 나름의 연말파티</t>
+  </si>
+  <si>
+    <t>제주의 바다거북 데이터를 함께 모아온 시민과학자와 함께 그간의 바다거북 데이터를 공유하고 시민과학활동이 해양생물 연구와 보전에 어떠한 의의가 있는지 전하는 자리를 마련했습니다. 관련 지식을 강연과 게임, 네트워킹으로 즐거운 시간을 함께하며 바다거북 시민과학프로젝트를 통해 유의미한 정보가 쌓여갈 수 있음에 고마움을 전달하는 뜻깊은 시간이었습니다.
+해양동물생태연구소 마크 MARC
+marckorea718.org
+기획, 진행 | 마크
+디자인 &amp; 운영 협력 | 한지인</t>
+  </si>
+  <si>
+    <t>남방큰돌고래와 함께 살기
+&lt;적정거리를 지켜요 2&gt;</t>
+  </si>
+  <si>
+    <t>인간의 활동 범위가 점점 넓어지며 야생동물과 우연히 혹은 의도적으로 접촉하게 되는 기회가 점점 많아지고 있습니다. 해양동물생태연구소 마크 MARC 는 인간이 남방큰돌고래를 포함한 해양생물과 건강하게 공존하기 위한 방법을 연구하고 ‘적정거리를 지켜요’ 캠페인을 통해 공개 배포하고 있습니다. 우리가 바다에서 꼭 지켜야 하는 다양한 행동 수칙을 전하는 인쇄물과 캠페인에 공감하는 분들을 위해 차량용 스티커, 마스킹 테이프를 굿즈로 제작했습니다.
+바다는 동물원이나 공원과 같은 관상용 공간이 아닌 힘껏 살아가는 모든 사람과 동식물 모두의 마을이라는 생각이 명확해지는 마크의 캠페인이 더욱 멀리 퍼져가기를 바랍니다.
+해양동물생태연구소 마크 MARC
+marckorea718.org
+기획 &amp; 콘텐츠 작성 | 마크
+디자인 | 한지인</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>제주 해안에서 남방큰돌고래를 연구하는 해양동물생태연구소 마크 MARC 의 생태예술전시에 함께했습니다. 인간과 바다를 공유하는 해양 야생동물인 남방큰돌고래를 오랫동안 바라보며 수집해온 시각/청각 데이터에 연구자들의 시선과 마음이 더해진 전시를 유인원 필드스테이션과 제주소통협력센터에서 두차례에 걸쳐 열었습니다. 낚싯줄에 얽힌 새끼 남방큰돌고래 ‘종달이’을 구조하기 위해 1년 8개월동안 밤낮없이 집중하던 중에 열린 전시라는 사실이 사람들에게 여러가지 마음을 선사했습니다. 종달이는 이제 만날 수 없지만, 제주에 서식하는 해양야생동물을 소중하게 여기는 사람들의 원이  계속해서 겹치고 겹쳐 더욱 크고 강인해지기를 바라며, 늘 함께하기를 약속합니다.
+해양동물생태연구소 마크 MARC
+marckorea718.org
+기획 | 마크
+소리 | 김명규
+인형 제작 &amp; 전시 디자인 &amp; 워크샵 진행 | 한지인
+협력 | 유인원 필드스테이션, 제주지역문제해결플랫폼</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -181,6 +223,12 @@
     <font>
       <sz val="9"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -572,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2E46E7-1DAD-934D-9C92-FF8655A6E484}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.83203125" style="2" customWidth="1"/>
@@ -657,137 +705,173 @@
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="C5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
+      <c r="B7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
         <v>3</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
+    <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
         <v>4</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2">
+    <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
         <v>5</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+    <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="3" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
